--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129914632</v>
+        <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>57966</v>
+        <v>92086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,39 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584506</v>
+        <v>584517</v>
       </c>
       <c r="R5" t="n">
-        <v>6401303</v>
+        <v>6401250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,17 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spelade upp läte och fick omedelbart svar. Efter ngn minut kom både 1 hane o 1 hona och var väldigt irriterade! Optimal biotop för arten.</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1118,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,39 +1130,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129914632</t>
+          <t>https://artportalen.se/Sighting/137197283</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129909609</v>
+        <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,12 +1170,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1194,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584485</v>
+        <v>584506</v>
       </c>
       <c r="R6" t="n">
-        <v>6401455</v>
+        <v>6401303</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,17 +1223,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosök i låga</t>
+          <t>Spelade upp läte och fick omedelbart svar. Efter ngn minut kom både 1 hane o 1 hona och var väldigt irriterade! Optimal biotop för arten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,19 +1253,19 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129909609</t>
+          <t>https://artportalen.se/Sighting/129914632</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129909677</v>
+        <v>129909609</v>
       </c>
       <c r="B7" t="n">
         <v>57950</v>
@@ -1309,13 +1308,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584443</v>
+        <v>584485</v>
       </c>
       <c r="R7" t="n">
-        <v>6401398</v>
+        <v>6401455</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår av födosök i barkborregran</t>
+          <t>Födosök i låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,50 +1374,46 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129909677</t>
+          <t>https://artportalen.se/Sighting/129909609</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129909597</v>
+        <v>129909677</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1428,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584537</v>
+        <v>584443</v>
       </c>
       <c r="R8" t="n">
-        <v>6401291</v>
+        <v>6401398</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,6 +1461,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår av födosök i barkborregran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1489,38 +1489,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129909597</t>
+          <t>https://artportalen.se/Sighting/129909677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129907509</v>
+        <v>129909597</v>
       </c>
       <c r="B9" t="n">
-        <v>99156</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1528,31 +1528,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ängnässjön, Sm</t>
+          <t>A 56968, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584488</v>
+        <v>584537</v>
       </c>
       <c r="R9" t="n">
-        <v>6401304</v>
+        <v>6401291</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,23 +1586,141 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909597</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129907509</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängnässjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>584488</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6401304</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129907509</t>
         </is>
@@ -1622,6 +1736,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92086</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92140</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>137197283</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
